--- a/salidas/empresas/DD.xlsx
+++ b/salidas/empresas/DD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.73948287963867</v>
+        <v>41.73949432373047</v>
       </c>
       <c r="C2" t="n">
         <v>75.57026672363281</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>42.45980072021484</v>
+        <v>42.45980834960938</v>
       </c>
       <c r="C3" t="n">
         <v>76.87443542480469</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>40.42571640014648</v>
+        <v>40.42570114135742</v>
       </c>
       <c r="C4" t="n">
         <v>72.53315734863281</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>40.43566513061523</v>
+        <v>40.43567276000977</v>
       </c>
       <c r="C5" t="n">
         <v>72.551025390625</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>39.6988525390625</v>
+        <v>39.69885635375977</v>
       </c>
       <c r="C6" t="n">
         <v>71.22899627685547</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>39.24928283691406</v>
+        <v>39.24927139282227</v>
       </c>
       <c r="C7" t="n">
         <v>69.72830963134766</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.34421157836914</v>
+        <v>38.34423828125</v>
       </c>
       <c r="C9" t="n">
         <v>68.12042999267578</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>39.57280349731445</v>
+        <v>39.57281494140625</v>
       </c>
       <c r="C10" t="n">
         <v>69.63898468017578</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>41.41033935546875</v>
+        <v>41.41032409667969</v>
       </c>
       <c r="C11" t="n">
         <v>72.87260437011719</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.61847305297852</v>
+        <v>40.61845779418945</v>
       </c>
       <c r="C12" t="n">
         <v>71.47911071777344</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.88763809204102</v>
+        <v>40.88764190673828</v>
       </c>
       <c r="C13" t="n">
         <v>71.2825927734375</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.56824111938477</v>
+        <v>42.56821441650391</v>
       </c>
       <c r="C14" t="n">
         <v>74.21250152587891</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>44.86367034912109</v>
+        <v>44.86369323730469</v>
       </c>
       <c r="C15" t="n">
         <v>78.21433258056641</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>47.37549591064453</v>
+        <v>47.37550735473633</v>
       </c>
       <c r="C16" t="n">
         <v>81.93031311035156</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>46.08418655395508</v>
+        <v>46.08420181274414</v>
       </c>
       <c r="C17" t="n">
         <v>79.69715118408203</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>46.87965774536133</v>
+        <v>46.879638671875</v>
       </c>
       <c r="C18" t="n">
         <v>81.07277679443359</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>45.33955001831055</v>
+        <v>45.33954620361328</v>
       </c>
       <c r="C20" t="n">
         <v>77.67836761474609</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>44.45318984985352</v>
+        <v>44.45320892333984</v>
       </c>
       <c r="C21" t="n">
         <v>76.15982055664062</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>45.33413314819336</v>
+        <v>45.33411407470703</v>
       </c>
       <c r="C22" t="n">
         <v>76.92802429199219</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.41870880126953</v>
+        <v>47.4187126159668</v>
       </c>
       <c r="C23" t="n">
         <v>80.46536254882812</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>44.15499496459961</v>
+        <v>44.15497207641602</v>
       </c>
       <c r="C24" t="n">
         <v>74.92711639404297</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>41.93227767944336</v>
+        <v>41.93228912353516</v>
       </c>
       <c r="C25" t="n">
         <v>70.42505645751953</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>41.10256958007812</v>
+        <v>41.10257339477539</v>
       </c>
       <c r="C26" t="n">
         <v>69.03156280517578</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>39.63881683349609</v>
+        <v>39.63879776000977</v>
       </c>
       <c r="C28" t="n">
         <v>65.83367156982422</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>43.18855285644531</v>
+        <v>43.18854904174805</v>
       </c>
       <c r="C29" t="n">
         <v>71.72922515869141</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>43.45745849609375</v>
+        <v>43.45746994018555</v>
       </c>
       <c r="C30" t="n">
         <v>72.17585754394531</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>37.98587799072266</v>
+        <v>37.98585891723633</v>
       </c>
       <c r="C31" t="n">
         <v>62.3677978515625</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>36.24489593505859</v>
+        <v>36.24490356445312</v>
       </c>
       <c r="C32" t="n">
         <v>59.50934982299805</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99850845336914</v>
+        <v>34.99851226806641</v>
       </c>
       <c r="C34" t="n">
         <v>56.77595520019531</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>29.38201713562012</v>
+        <v>29.38202667236328</v>
       </c>
       <c r="C35" t="n">
         <v>47.66464996337891</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.42865371704102</v>
+        <v>20.42865562438965</v>
       </c>
       <c r="C36" t="n">
         <v>33.14015197753906</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.98714256286621</v>
+        <v>16.98715019226074</v>
       </c>
       <c r="C37" t="n">
         <v>26.95875358581543</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.04711437225342</v>
+        <v>13.04712104797363</v>
       </c>
       <c r="C38" t="n">
         <v>20.70589447021484</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.060169219970703</v>
+        <v>8.060172080993652</v>
       </c>
       <c r="C39" t="n">
         <v>12.7915620803833</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.644227027893066</v>
+        <v>9.644227981567383</v>
       </c>
       <c r="C40" t="n">
         <v>15.06045722961426</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>18.30457878112793</v>
+        <v>18.3045825958252</v>
       </c>
       <c r="C41" t="n">
         <v>28.58449745178223</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.22656059265137</v>
+        <v>20.22656631469727</v>
       </c>
       <c r="C42" t="n">
         <v>31.58586883544922</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>18.64082908630371</v>
+        <v>18.64082717895508</v>
       </c>
       <c r="C43" t="n">
         <v>28.8346118927002</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.27986907958984</v>
+        <v>27.27986335754395</v>
       </c>
       <c r="C47" t="n">
         <v>41.94775009155273</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>32.2757568359375</v>
+        <v>32.2757453918457</v>
       </c>
       <c r="C48" t="n">
         <v>49.62983322143555</v>
@@ -1375,7 +1387,7 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>31.64055252075195</v>
+        <v>31.64056205749512</v>
       </c>
       <c r="C50" t="n">
         <v>48.39712524414062</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>33.06550216674805</v>
+        <v>33.06549835205078</v>
       </c>
       <c r="C51" t="n">
         <v>50.57669448852539</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>34.71035003662109</v>
+        <v>34.71035385131836</v>
       </c>
       <c r="C52" t="n">
         <v>52.82772445678711</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>36.18938827514648</v>
+        <v>36.18939208984375</v>
       </c>
       <c r="C53" t="n">
         <v>55.07875442504883</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>31.58794975280762</v>
+        <v>31.58796119689941</v>
       </c>
       <c r="C54" t="n">
         <v>48.0755500793457</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.0092658996582</v>
+        <v>28.00926780700684</v>
       </c>
       <c r="C55" t="n">
         <v>42.37651824951172</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.27206802368164</v>
+        <v>32.27209091186523</v>
       </c>
       <c r="C56" t="n">
         <v>48.82589340209961</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>28.77681732177734</v>
+        <v>28.77682304382324</v>
       </c>
       <c r="C57" t="n">
         <v>43.53776168823242</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>32.60072326660156</v>
+        <v>32.60072708129883</v>
       </c>
       <c r="C58" t="n">
         <v>49.05814361572266</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>36.61350250244141</v>
+        <v>36.61349105834961</v>
       </c>
       <c r="C59" t="n">
         <v>55.09661865234375</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>37.01713562011719</v>
+        <v>37.01714324951172</v>
       </c>
       <c r="C60" t="n">
         <v>55.70404052734375</v>
@@ -1603,11 +1615,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>40.70888137817383</v>
+        <v>40.70889282226562</v>
       </c>
       <c r="C61" t="n">
         <v>60.99217224121094</v>
@@ -1622,11 +1634,11 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>42.30671691894531</v>
+        <v>42.30672073364258</v>
       </c>
       <c r="C62" t="n">
         <v>63.38612365722656</v>
@@ -1641,11 +1653,11 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>44.30997085571289</v>
+        <v>44.30997467041016</v>
       </c>
       <c r="C63" t="n">
         <v>66.38749694824219</v>
@@ -1660,11 +1672,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>45.19652938842773</v>
+        <v>45.19652557373047</v>
       </c>
       <c r="C64" t="n">
         <v>67.44155120849609</v>
@@ -1679,11 +1691,11 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>49.07564926147461</v>
+        <v>49.07563781738281</v>
       </c>
       <c r="C65" t="n">
         <v>73.22991180419922</v>
@@ -1698,11 +1710,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.25695037841797</v>
+        <v>43.2569694519043</v>
       </c>
       <c r="C66" t="n">
         <v>64.54736328125</v>
@@ -1717,7 +1729,7 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1736,7 +1748,7 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1755,11 +1767,11 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>34.30627822875977</v>
+        <v>34.3062858581543</v>
       </c>
       <c r="C69" t="n">
         <v>50.82680892944336</v>
@@ -1774,7 +1786,7 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1793,11 +1805,11 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>33.95064926147461</v>
+        <v>33.95063400268555</v>
       </c>
       <c r="C71" t="n">
         <v>49.80848693847656</v>
@@ -1812,7 +1824,7 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -1831,11 +1843,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>35.3284912109375</v>
+        <v>35.32849502563477</v>
       </c>
       <c r="C73" t="n">
         <v>51.38063430786133</v>
@@ -1850,11 +1862,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.16335296630859</v>
+        <v>41.16335678100586</v>
       </c>
       <c r="C74" t="n">
         <v>59.86665725708008</v>
@@ -1869,11 +1881,11 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>41.16335296630859</v>
+        <v>41.16335678100586</v>
       </c>
       <c r="C75" t="n">
         <v>59.86665725708008</v>
@@ -1888,11 +1900,11 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.85616302490234</v>
+        <v>42.85614776611328</v>
       </c>
       <c r="C76" t="n">
         <v>61.88543701171875</v>
@@ -1907,11 +1919,11 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>41.9158821105957</v>
+        <v>41.91590118408203</v>
       </c>
       <c r="C77" t="n">
         <v>60.52767181396484</v>
@@ -1926,11 +1938,11 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>38.42701721191406</v>
+        <v>38.42702484130859</v>
       </c>
       <c r="C78" t="n">
         <v>55.48965454101562</v>
@@ -1945,11 +1957,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>39.3736686706543</v>
+        <v>39.37367248535156</v>
       </c>
       <c r="C79" t="n">
         <v>56.27573013305664</v>
@@ -1964,7 +1976,7 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -1983,11 +1995,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.63626480102539</v>
+        <v>36.63625717163086</v>
       </c>
       <c r="C81" t="n">
         <v>52.36322784423828</v>
@@ -2002,11 +2014,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>36.59184646606445</v>
+        <v>36.59184265136719</v>
       </c>
       <c r="C82" t="n">
         <v>51.73794174194336</v>
@@ -2021,11 +2033,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>37.02144241333008</v>
+        <v>37.02144622802734</v>
       </c>
       <c r="C83" t="n">
         <v>52.34535980224609</v>
@@ -2040,11 +2052,11 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>38.14598846435547</v>
+        <v>38.14596557617188</v>
       </c>
       <c r="C84" t="n">
         <v>53.93537139892578</v>
@@ -2059,11 +2071,11 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>41.25703811645508</v>
+        <v>41.25703430175781</v>
       </c>
       <c r="C85" t="n">
         <v>57.75854873657227</v>
@@ -2078,7 +2090,7 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2097,11 +2109,11 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>40.47862243652344</v>
+        <v>40.47859954833984</v>
       </c>
       <c r="C87" t="n">
         <v>56.66876602172852</v>
@@ -2116,11 +2128,11 @@
       <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>41.0384407043457</v>
+        <v>41.03843688964844</v>
       </c>
       <c r="C88" t="n">
         <v>56.88314819335938</v>
@@ -2135,11 +2147,11 @@
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>43.70645523071289</v>
+        <v>43.70644760131836</v>
       </c>
       <c r="C89" t="n">
         <v>60.58126831054688</v>
@@ -2154,11 +2166,11 @@
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.41534805297852</v>
+        <v>44.41533279418945</v>
       </c>
       <c r="C90" t="n">
         <v>61.56386184692383</v>
@@ -2173,11 +2185,11 @@
       <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>41.8760986328125</v>
+        <v>41.87609481811523</v>
       </c>
       <c r="C91" t="n">
         <v>57.47270584106445</v>
@@ -2192,11 +2204,11 @@
       <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>45.61200714111328</v>
+        <v>45.61200332641602</v>
       </c>
       <c r="C92" t="n">
         <v>62.60004806518555</v>
@@ -2211,7 +2223,7 @@
       <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2230,11 +2242,11 @@
       <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.39031219482422</v>
+        <v>50.39030075073242</v>
       </c>
       <c r="C94" t="n">
         <v>68.60279083251953</v>
@@ -2249,11 +2261,11 @@
       <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>51.79438400268555</v>
+        <v>51.79440307617188</v>
       </c>
       <c r="C95" t="n">
         <v>70.51438140869141</v>
@@ -2268,11 +2280,11 @@
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.25637054443359</v>
+        <v>51.25638961791992</v>
       </c>
       <c r="C96" t="n">
         <v>69.78190612792969</v>
@@ -2287,11 +2299,11 @@
       <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>58.68234252929688</v>
+        <v>58.68236923217773</v>
       </c>
       <c r="C97" t="n">
         <v>79.32197570800781</v>
@@ -2306,11 +2318,11 @@
       <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>60.14944076538086</v>
+        <v>60.14943313598633</v>
       </c>
       <c r="C98" t="n">
         <v>81.30503082275391</v>
@@ -2325,11 +2337,11 @@
       <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>64.37881469726562</v>
+        <v>64.37880706787109</v>
       </c>
       <c r="C99" t="n">
         <v>87.02192687988281</v>
@@ -2344,11 +2356,11 @@
       <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>64.70453643798828</v>
+        <v>64.70454406738281</v>
       </c>
       <c r="C100" t="n">
         <v>86.80754089355469</v>
@@ -2363,11 +2375,11 @@
       <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>66.44901275634766</v>
+        <v>66.44900512695312</v>
       </c>
       <c r="C101" t="n">
         <v>89.14790344238281</v>
@@ -2382,11 +2394,11 @@
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>69.40525054931641</v>
+        <v>69.40522766113281</v>
       </c>
       <c r="C102" t="n">
         <v>93.11399841308594</v>
@@ -2401,7 +2413,7 @@
       <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2420,11 +2432,11 @@
       <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>68.48870086669922</v>
+        <v>68.48869323730469</v>
       </c>
       <c r="C104" t="n">
         <v>91.23814392089844</v>
@@ -2439,11 +2451,11 @@
       <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>71.81452941894531</v>
+        <v>71.81455993652344</v>
       </c>
       <c r="C105" t="n">
         <v>95.66873931884766</v>
@@ -2458,11 +2470,11 @@
       <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.81913757324219</v>
+        <v>70.81914520263672</v>
       </c>
       <c r="C106" t="n">
         <v>93.68569183349609</v>
@@ -2477,11 +2489,11 @@
       <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>66.71369171142578</v>
+        <v>66.71372222900391</v>
       </c>
       <c r="C107" t="n">
         <v>88.254638671875</v>
@@ -2496,11 +2508,11 @@
       <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.72785949707031</v>
+        <v>65.72782897949219</v>
       </c>
       <c r="C108" t="n">
         <v>86.95046997070312</v>
@@ -2515,11 +2527,11 @@
       <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>62.15702438354492</v>
+        <v>62.15701293945312</v>
       </c>
       <c r="C109" t="n">
         <v>81.48368072509766</v>
@@ -2534,11 +2546,11 @@
       <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>61.54380416870117</v>
+        <v>61.54378128051758</v>
       </c>
       <c r="C110" t="n">
         <v>80.67974090576172</v>
@@ -2553,11 +2565,11 @@
       <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>67.10397338867188</v>
+        <v>67.10398864746094</v>
       </c>
       <c r="C111" t="n">
         <v>87.96878814697266</v>
@@ -2572,11 +2584,11 @@
       <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>65.97819519042969</v>
+        <v>65.97818756103516</v>
       </c>
       <c r="C112" t="n">
         <v>85.71775817871094</v>
@@ -2591,11 +2603,11 @@
       <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>70.13105773925781</v>
+        <v>70.13105010986328</v>
       </c>
       <c r="C113" t="n">
         <v>91.11308288574219</v>
@@ -2610,11 +2622,11 @@
       <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>71.60242462158203</v>
+        <v>71.60247039794922</v>
       </c>
       <c r="C114" t="n">
         <v>93.02467346191406</v>
@@ -2629,7 +2641,7 @@
       <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -2648,11 +2660,11 @@
       <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>65.22784423828125</v>
+        <v>65.22786712646484</v>
       </c>
       <c r="C116" t="n">
         <v>84.07415008544922</v>
@@ -2667,11 +2679,11 @@
       <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>60.65387344360352</v>
+        <v>60.65386962890625</v>
       </c>
       <c r="C117" t="n">
         <v>78.17859649658203</v>
@@ -2686,11 +2698,11 @@
       <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>59.35792541503906</v>
+        <v>59.3579216003418</v>
       </c>
       <c r="C118" t="n">
         <v>75.74891662597656</v>
@@ -2705,11 +2717,11 @@
       <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>72.33546447753906</v>
+        <v>72.33545684814453</v>
       </c>
       <c r="C119" t="n">
         <v>92.31005859375</v>
@@ -2724,11 +2736,11 @@
       <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>72.97944641113281</v>
+        <v>72.97943878173828</v>
       </c>
       <c r="C120" t="n">
         <v>93.13186645507812</v>
@@ -2743,11 +2755,11 @@
       <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>72.70986175537109</v>
+        <v>72.70982360839844</v>
       </c>
       <c r="C121" t="n">
         <v>91.97061920166016</v>
@@ -2762,11 +2774,11 @@
       <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>59.32039642333984</v>
+        <v>59.32037734985352</v>
       </c>
       <c r="C122" t="n">
         <v>75.0343017578125</v>
@@ -2781,11 +2793,11 @@
       <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>68.65628051757812</v>
+        <v>68.65629577636719</v>
       </c>
       <c r="C123" t="n">
         <v>86.84327697753906</v>
@@ -2800,7 +2812,7 @@
       <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -2819,11 +2831,11 @@
       <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>74.97475433349609</v>
+        <v>74.97476196289062</v>
       </c>
       <c r="C125" t="n">
         <v>93.98940277099609</v>
@@ -2838,11 +2850,11 @@
       <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>73.19335174560547</v>
+        <v>73.19337463378906</v>
       </c>
       <c r="C126" t="n">
         <v>91.75623321533203</v>
@@ -2857,11 +2869,11 @@
       <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>71.50010681152344</v>
+        <v>71.50013732910156</v>
       </c>
       <c r="C127" t="n">
         <v>88.80845642089844</v>
@@ -2876,11 +2888,11 @@
       <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>77.19599151611328</v>
+        <v>77.19596862792969</v>
       </c>
       <c r="C128" t="n">
         <v>95.88312530517578</v>
@@ -2895,11 +2907,11 @@
       <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>77.15284729003906</v>
+        <v>77.15281677246094</v>
       </c>
       <c r="C129" t="n">
         <v>95.82952880859375</v>
@@ -2914,11 +2926,11 @@
       <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>75.20751953125</v>
+        <v>75.20750427246094</v>
       </c>
       <c r="C130" t="n">
         <v>92.59590148925781</v>
@@ -2933,11 +2945,11 @@
       <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>78.08057403564453</v>
+        <v>78.08059692382812</v>
       </c>
       <c r="C131" t="n">
         <v>96.13323974609375</v>
@@ -2952,11 +2964,11 @@
       <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>80.85205841064453</v>
+        <v>80.85206604003906</v>
       </c>
       <c r="C132" t="n">
         <v>99.54550933837891</v>
@@ -2971,11 +2983,11 @@
       <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>83.68388366699219</v>
+        <v>83.68385314941406</v>
       </c>
       <c r="C133" t="n">
         <v>102.2253112792969</v>
@@ -2990,11 +3002,11 @@
       <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>87.20846557617188</v>
+        <v>87.20845794677734</v>
       </c>
       <c r="C134" t="n">
         <v>106.5308456420898</v>
@@ -3009,11 +3021,11 @@
       <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>91.0548095703125</v>
+        <v>91.05482482910156</v>
       </c>
       <c r="C135" t="n">
         <v>111.2294235229492</v>
@@ -3028,11 +3040,11 @@
       <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>93.58911895751953</v>
+        <v>93.58914184570312</v>
       </c>
       <c r="C136" t="n">
         <v>113.5161819458008</v>
@@ -3047,11 +3059,11 @@
       <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>92.49916076660156</v>
+        <v>92.49917602539062</v>
       </c>
       <c r="C137" t="n">
         <v>112.1941528320312</v>
@@ -3066,7 +3078,7 @@
       <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3085,7 +3097,7 @@
       <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3104,11 +3116,11 @@
       <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>95.97987365722656</v>
+        <v>95.97986602783203</v>
       </c>
       <c r="C140" t="n">
         <v>114.7667541503906</v>
@@ -3123,11 +3135,11 @@
       <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>99.58061981201172</v>
+        <v>99.58058166503906</v>
       </c>
       <c r="C141" t="n">
         <v>119.0722961425781</v>
@@ -3142,11 +3154,11 @@
       <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>103.4353332519531</v>
+        <v>103.4353256225586</v>
       </c>
       <c r="C142" t="n">
         <v>123.6815490722656</v>
@@ -3161,7 +3173,7 @@
       <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -3180,11 +3192,11 @@
       <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>108.0971755981445</v>
+        <v>108.09716796875</v>
       </c>
       <c r="C144" t="n">
         <v>128.5587768554688</v>
@@ -3205,7 +3217,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -3230,7 +3242,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -3255,7 +3267,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -3280,11 +3292,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>96.19773101806641</v>
+        <v>96.19773864746094</v>
       </c>
       <c r="C148" t="n">
         <v>113.8198928833008</v>
@@ -3305,11 +3317,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>95.48805999755859</v>
+        <v>95.48807525634766</v>
       </c>
       <c r="C149" t="n">
         <v>112.980224609375</v>
@@ -3330,11 +3342,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>97.38047027587891</v>
+        <v>97.38043212890625</v>
       </c>
       <c r="C150" t="n">
         <v>114.5345077514648</v>
@@ -3355,7 +3367,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -3380,11 +3392,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>104.4588165283203</v>
+        <v>104.4587936401367</v>
       </c>
       <c r="C152" t="n">
         <v>122.8597412109375</v>
@@ -3405,11 +3417,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>107.0942306518555</v>
+        <v>107.0942230224609</v>
       </c>
       <c r="C153" t="n">
         <v>125.289421081543</v>
@@ -3434,11 +3446,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>98.20663452148438</v>
+        <v>98.20658874511719</v>
       </c>
       <c r="C154" t="n">
         <v>114.8918151855469</v>
@@ -3463,11 +3475,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>82.34024047851562</v>
+        <v>82.34025573730469</v>
       </c>
       <c r="C155" t="n">
         <v>96.32975769042969</v>
@@ -3492,7 +3504,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -3521,11 +3533,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>82.21431732177734</v>
+        <v>82.21429443359375</v>
       </c>
       <c r="C157" t="n">
         <v>95.54367828369141</v>
@@ -3550,11 +3562,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>82.72164154052734</v>
+        <v>82.72161102294922</v>
       </c>
       <c r="C158" t="n">
         <v>96.13323974609375</v>
@@ -3579,11 +3591,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>82.39026641845703</v>
+        <v>82.39027404785156</v>
       </c>
       <c r="C159" t="n">
         <v>95.0970458984375</v>
@@ -3608,7 +3620,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -3637,11 +3649,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>88.49663543701172</v>
+        <v>88.49662017822266</v>
       </c>
       <c r="C161" t="n">
         <v>102.1451797485352</v>
@@ -3666,11 +3678,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>70.50951385498047</v>
+        <v>70.50948333740234</v>
       </c>
       <c r="C162" t="n">
         <v>81.07856750488281</v>
@@ -3695,7 +3707,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -3724,11 +3736,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>79.09474945068359</v>
+        <v>79.09474182128906</v>
       </c>
       <c r="C164" t="n">
         <v>90.57740783691406</v>
@@ -3753,11 +3765,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>74.45823669433594</v>
+        <v>74.45822906494141</v>
       </c>
       <c r="C165" t="n">
         <v>85.26778411865234</v>
@@ -3782,11 +3794,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>78.16306304931641</v>
+        <v>78.16307830810547</v>
       </c>
       <c r="C166" t="n">
         <v>89.51045989990234</v>
@@ -3811,7 +3823,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -3840,7 +3852,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -3898,11 +3910,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>56.35836410522461</v>
+        <v>56.35836791992188</v>
       </c>
       <c r="C170" t="n">
         <v>64.24267578125</v>
@@ -3927,11 +3939,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.54238128662109</v>
+        <v>47.54239654541016</v>
       </c>
       <c r="C171" t="n">
         <v>53.84937286376953</v>
@@ -3956,7 +3968,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -3985,7 +3997,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4014,11 +4026,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>56.56277847290039</v>
+        <v>56.56278610229492</v>
       </c>
       <c r="C174" t="n">
         <v>63.67782211303711</v>
@@ -4041,11 +4053,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>59.23872756958008</v>
+        <v>59.23871994018555</v>
       </c>
       <c r="C175" t="n">
         <v>66.69037628173828</v>
@@ -4068,11 +4080,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>59.95292282104492</v>
+        <v>59.95292663574219</v>
       </c>
       <c r="C176" t="n">
         <v>67.12970733642578</v>
@@ -4095,11 +4107,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>62.50888824462891</v>
+        <v>62.50886154174805</v>
       </c>
       <c r="C177" t="n">
         <v>69.99163055419922</v>
@@ -4122,11 +4134,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>62.19499969482422</v>
+        <v>62.19499588012695</v>
       </c>
       <c r="C178" t="n">
         <v>69.64016723632812</v>
@@ -4149,11 +4161,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>63.76445770263672</v>
+        <v>63.76443481445312</v>
       </c>
       <c r="C179" t="n">
         <v>71.39749145507812</v>
@@ -4176,11 +4188,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>71.44876098632812</v>
+        <v>71.44876861572266</v>
       </c>
       <c r="C180" t="n">
         <v>79.63179779052734</v>
@@ -4203,11 +4215,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>80.08702850341797</v>
+        <v>80.0870361328125</v>
       </c>
       <c r="C181" t="n">
         <v>89.25941467285156</v>
@@ -4230,11 +4242,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>89.47989654541016</v>
+        <v>89.47987365722656</v>
       </c>
       <c r="C182" t="n">
         <v>99.72803497314453</v>
@@ -4257,11 +4269,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>79.53938293457031</v>
+        <v>79.53939819335938</v>
       </c>
       <c r="C183" t="n">
         <v>88.26778411865234</v>
@@ -4284,11 +4296,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>87.41190338134766</v>
+        <v>87.41189575195312</v>
       </c>
       <c r="C184" t="n">
         <v>97.00418090820312</v>
@@ -4311,11 +4323,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>87.2196044921875</v>
+        <v>87.21959686279297</v>
       </c>
       <c r="C185" t="n">
         <v>96.79079437255859</v>
@@ -4338,11 +4350,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>96.02507019042969</v>
+        <v>96.02507781982422</v>
       </c>
       <c r="C186" t="n">
         <v>106.1799163818359</v>
@@ -4367,11 +4379,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>87.87445831298828</v>
+        <v>87.87448120117188</v>
       </c>
       <c r="C187" t="n">
         <v>97.16736602783203</v>
@@ -4396,7 +4408,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -4425,11 +4437,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>84.36707305908203</v>
+        <v>84.3670654296875</v>
       </c>
       <c r="C189" t="n">
         <v>92.91213226318359</v>
@@ -4454,11 +4466,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>77.49414825439453</v>
+        <v>77.494140625</v>
       </c>
       <c r="C190" t="n">
         <v>85.34309387207031</v>
@@ -4483,11 +4495,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>79.3292236328125</v>
+        <v>79.32920837402344</v>
       </c>
       <c r="C191" t="n">
         <v>87.364013671875</v>
@@ -4512,11 +4524,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>84.62858581542969</v>
+        <v>84.62857818603516</v>
       </c>
       <c r="C192" t="n">
         <v>92.83682250976562</v>
@@ -4541,11 +4553,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>92.43234252929688</v>
+        <v>92.43235778808594</v>
       </c>
       <c r="C193" t="n">
         <v>101.3974914550781</v>
@@ -4570,7 +4582,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -4599,11 +4611,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>88.91876220703125</v>
+        <v>88.91876983642578</v>
       </c>
       <c r="C195" t="n">
         <v>97.11715698242188</v>
@@ -4628,7 +4640,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -4657,11 +4669,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>75.77114105224609</v>
+        <v>75.77117156982422</v>
       </c>
       <c r="C197" t="n">
         <v>82.75732421875</v>
@@ -4686,11 +4698,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>78.36157989501953</v>
+        <v>78.36159515380859</v>
       </c>
       <c r="C198" t="n">
         <v>85.16736602783203</v>
@@ -4715,11 +4727,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>64.190673828125</v>
+        <v>64.19068145751953</v>
       </c>
       <c r="C199" t="n">
         <v>69.76569366455078</v>
@@ -4744,11 +4756,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>71.11085510253906</v>
+        <v>71.11083984375</v>
       </c>
       <c r="C200" t="n">
         <v>76.85774230957031</v>
@@ -4773,7 +4785,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -4802,11 +4814,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.53318786621094</v>
+        <v>58.53318405151367</v>
       </c>
       <c r="C202" t="n">
         <v>63.26359939575195</v>
@@ -4831,7 +4843,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -4860,11 +4872,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>82.27993011474609</v>
+        <v>82.2799072265625</v>
       </c>
       <c r="C204" t="n">
         <v>88.50627899169922</v>
@@ -4889,7 +4901,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -4918,11 +4930,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>86.29413604736328</v>
+        <v>86.29414367675781</v>
       </c>
       <c r="C206" t="n">
         <v>92.82426452636719</v>
@@ -4947,11 +4959,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>85.64339447021484</v>
+        <v>85.64338684082031</v>
       </c>
       <c r="C207" t="n">
         <v>91.66945648193359</v>
@@ -4976,11 +4988,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>84.16576385498047</v>
+        <v>84.165771484375</v>
       </c>
       <c r="C208" t="n">
         <v>90.08786773681641</v>
@@ -5005,11 +5017,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>81.76168060302734</v>
+        <v>81.76168823242188</v>
       </c>
       <c r="C209" t="n">
         <v>87.51464080810547</v>
@@ -5034,7 +5046,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5063,7 +5075,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5092,7 +5104,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5121,11 +5133,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>91.07420349121094</v>
+        <v>91.07418060302734</v>
       </c>
       <c r="C213" t="n">
         <v>96.51464080810547</v>
@@ -5150,11 +5162,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>88.34992218017578</v>
+        <v>88.34990692138672</v>
       </c>
       <c r="C214" t="n">
         <v>93.62761688232422</v>
@@ -5179,11 +5191,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>86.32445526123047</v>
+        <v>86.32447052001953</v>
       </c>
       <c r="C215" t="n">
         <v>91.48117065429688</v>
@@ -5208,11 +5220,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>85.16735076904297</v>
+        <v>85.16733551025391</v>
       </c>
       <c r="C216" t="n">
         <v>89.79916381835938</v>
@@ -5237,7 +5249,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -5266,11 +5278,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>73.57201385498047</v>
+        <v>73.57199859619141</v>
       </c>
       <c r="C218" t="n">
         <v>77.57321929931641</v>
@@ -5295,11 +5307,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>82.8218994140625</v>
+        <v>82.82188415527344</v>
       </c>
       <c r="C219" t="n">
         <v>86.84937286376953</v>
@@ -5324,11 +5336,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>91.77559661865234</v>
+        <v>91.77560424804688</v>
       </c>
       <c r="C220" t="n">
         <v>96.23849487304688</v>
@@ -5353,11 +5365,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>86.78402709960938</v>
+        <v>86.78401947021484</v>
       </c>
       <c r="C221" t="n">
         <v>91.00418090820312</v>
@@ -5382,11 +5394,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>98.80614471435547</v>
+        <v>98.80613708496094</v>
       </c>
       <c r="C222" t="n">
         <v>103.1297073364258</v>
@@ -5411,11 +5423,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>96.79779815673828</v>
+        <v>96.79778289794922</v>
       </c>
       <c r="C223" t="n">
         <v>101.0334701538086</v>
@@ -5440,11 +5452,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>100.6581573486328</v>
+        <v>100.6581497192383</v>
       </c>
       <c r="C224" t="n">
         <v>105.0627593994141</v>
@@ -5469,11 +5481,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>101.7832489013672</v>
+        <v>101.7832565307617</v>
       </c>
       <c r="C225" t="n">
         <v>105.7531356811523</v>
@@ -5498,7 +5510,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -5527,11 +5539,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>100.2610244750977</v>
+        <v>100.2610321044922</v>
       </c>
       <c r="C227" t="n">
         <v>104.1715469360352</v>
@@ -5556,7 +5568,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -5585,11 +5597,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>92.53748321533203</v>
+        <v>92.53749084472656</v>
       </c>
       <c r="C229" t="n">
         <v>95.71129608154297</v>
@@ -5614,7 +5626,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -5643,7 +5655,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -5672,11 +5684,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>91.08885192871094</v>
+        <v>91.08883666992188</v>
       </c>
       <c r="C232" t="n">
         <v>93.74058532714844</v>
@@ -5701,11 +5713,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>80.48946380615234</v>
+        <v>80.48945617675781</v>
       </c>
       <c r="C233" t="n">
         <v>82.83263397216797</v>
@@ -5730,11 +5742,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>81.96461486816406</v>
+        <v>81.96460723876953</v>
       </c>
       <c r="C234" t="n">
         <v>83.84937286376953</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>84.16097259521484</v>
+        <v>84.16098022460938</v>
       </c>
       <c r="C235" t="n">
         <v>86.09623718261719</v>
@@ -5784,7 +5796,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -5811,7 +5823,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -5838,7 +5850,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -5865,11 +5877,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>100.7177276611328</v>
+        <v>100.7177200317383</v>
       </c>
       <c r="C239" t="n">
         <v>102.4895401000977</v>
@@ -5892,7 +5904,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -5946,7 +5958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -5973,11 +5985,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>148.2766876220703</v>
+        <v>148.2766723632812</v>
       </c>
       <c r="C243" t="n">
         <v>150.1199951171875</v>
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>136.2574615478516</v>
+        <v>136.2574462890625</v>
       </c>
       <c r="C244" t="n">
         <v>137.3999938964844</v>
@@ -6027,7 +6039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6054,7 +6066,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6081,7 +6093,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6108,7 +6120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6135,7 +6147,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6164,32 +6176,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>130.8800048828125</v>
+        <v>130.2200012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>130.8800048828125</v>
+        <v>130.2200012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>19693400</v>
+        <v>20503300</v>
       </c>
       <c r="E250" t="n">
         <v>0.4500000000000003</v>
       </c>
       <c r="F250" t="n">
-        <v>290.8444552951387</v>
+        <v>289.3777804904512</v>
       </c>
       <c r="G250" t="n">
         <v>135042975</v>
       </c>
       <c r="H250" t="n">
-        <v>17674425227.38953</v>
+        <v>17585296369.34738</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1458306142914876</v>
+        <v>0.1518279643942974</v>
       </c>
     </row>
   </sheetData>
@@ -6221,75 +6233,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6325,13 +6337,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6367,13 +6379,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6409,13 +6421,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6442,7 +6454,7 @@
       <c r="I5" t="n">
         <v>4.406114949779131</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K5" t="n">
@@ -6455,13 +6467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6488,7 +6500,7 @@
       <c r="I6" t="n">
         <v>3.852290319509551</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K6" t="n">
@@ -6501,13 +6513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6534,7 +6546,7 @@
       <c r="I7" t="n">
         <v>2.357660933683086</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K7" t="n">
@@ -6547,13 +6559,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6580,7 +6592,7 @@
       <c r="I8" t="n">
         <v>1.911028167336651</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K8" t="n">
@@ -6593,13 +6605,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6626,7 +6638,7 @@
       <c r="I9" t="n">
         <v>1.357203537067071</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K9" t="n">
@@ -6639,13 +6651,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6672,7 +6684,7 @@
       <c r="I10" t="n">
         <v>1.16068511987464</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K10" t="n">
@@ -6685,13 +6697,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>43507</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6718,7 +6730,7 @@
       <c r="I11" t="n">
         <v>2.947776257886473</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>43507</v>
       </c>
       <c r="K11" t="n">
@@ -6731,13 +6743,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6764,7 +6776,7 @@
       <c r="I12" t="n">
         <v>2.719118146827753</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K12" t="n">
@@ -6777,13 +6789,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6810,7 +6822,7 @@
       <c r="I13" t="n">
         <v>0.4073796417370993</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K13" t="n">
@@ -6823,13 +6835,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6856,7 +6868,7 @@
       <c r="I14" t="n">
         <v>0.6598231807675998</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K14" t="n">
@@ -6869,13 +6881,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6902,7 +6914,7 @@
       <c r="I15" t="n">
         <v>0.8410041841004184</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K15" t="n">
@@ -6915,13 +6927,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6948,7 +6960,7 @@
       <c r="I16" t="n">
         <v>-0.8118483097562595</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K16" t="n">
@@ -6961,13 +6973,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6994,7 +7006,7 @@
       <c r="I17" t="n">
         <v>-4.087998937371323</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K17" t="n">
@@ -7007,13 +7019,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7040,7 +7052,7 @@
       <c r="I18" t="n">
         <v>-4.853689313940361</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K18" t="n">
@@ -7053,13 +7065,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7086,7 +7098,7 @@
       <c r="I19" t="n">
         <v>-5.03347280334728</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K19" t="n">
@@ -7099,13 +7111,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7132,7 +7144,7 @@
       <c r="I20" t="n">
         <v>7.179916317991634</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K20" t="n">
@@ -7145,13 +7157,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7178,7 +7190,7 @@
       <c r="I21" t="n">
         <v>12.5397489539749</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K21" t="n">
@@ -7191,13 +7203,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7224,7 +7236,7 @@
       <c r="I22" t="n">
         <v>13.61924686192469</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K22" t="n">
@@ -7237,13 +7249,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7270,7 +7282,7 @@
       <c r="I23" t="n">
         <v>14.92468619246862</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K23" t="n">
@@ -7283,13 +7295,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7316,7 +7328,7 @@
       <c r="I24" t="n">
         <v>4.945606694560667</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="K24" t="n">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7362,7 +7374,7 @@
       <c r="I25" t="n">
         <v>5.761506276150626</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K25" t="n">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7408,7 +7420,7 @@
       <c r="I26" t="n">
         <v>5.736401673640166</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="K26" t="n">
@@ -7421,13 +7433,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7454,7 +7466,7 @@
       <c r="I27" t="n">
         <v>14.7489539748954</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="K27" t="n">
@@ -7467,13 +7479,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7500,7 +7512,7 @@
       <c r="I28" t="n">
         <v>14.25941422594142</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K28" t="n">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7546,7 +7558,7 @@
       <c r="I29" t="n">
         <v>11.96234309623431</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K29" t="n">
@@ -7559,13 +7571,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7592,7 +7604,7 @@
       <c r="I30" t="n">
         <v>11.92468619246862</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K30" t="n">
@@ -7605,13 +7617,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7638,7 +7650,7 @@
       <c r="I31" t="n">
         <v>1.179916317991632</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K31" t="n">
@@ -7651,13 +7663,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7684,7 +7696,7 @@
       <c r="I32" t="n">
         <v>1.0418410041841</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K32" t="n">
@@ -7697,13 +7709,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -7730,7 +7742,7 @@
       <c r="I33" t="n">
         <v>1.920502092050209</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K33" t="n">
@@ -7743,13 +7755,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7776,7 +7788,7 @@
       <c r="I34" t="n">
         <v>2.397489539748954</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="K34" t="n">
@@ -7789,13 +7801,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7822,7 +7834,7 @@
       <c r="I35" t="n">
         <v>2.096234309623431</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K35" t="n">
@@ -7835,13 +7847,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7868,7 +7880,7 @@
       <c r="I36" t="n">
         <v>-0.238493723849373</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K36" t="n">
@@ -7881,13 +7893,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7914,7 +7926,7 @@
       <c r="I37" t="n">
         <v>-0.5899581589958164</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K37" t="n">
@@ -7927,13 +7939,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7960,7 +7972,7 @@
       <c r="I38" t="n">
         <v>-2.81560669456067</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K38" t="n">
@@ -7973,13 +7985,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8006,7 +8018,7 @@
       <c r="I39" t="n">
         <v>-3.364142259414226</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K39" t="n">
@@ -8019,13 +8031,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8052,7 +8064,7 @@
       <c r="I40" t="n">
         <v>-0.424267782426778</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K40" t="n">
@@ -8065,13 +8077,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8098,7 +8110,7 @@
       <c r="I41" t="n">
         <v>0.4500000000000003</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K41" t="n">
@@ -8135,52 +8147,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="C2" t="n">
@@ -8209,10 +8221,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C3" t="n">
@@ -8241,10 +8253,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C4" t="n">
@@ -8273,10 +8285,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C5" t="n">
@@ -8305,10 +8317,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C6" t="n">
@@ -8337,10 +8349,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43507</v>
       </c>
       <c r="C7" t="n">
@@ -8369,10 +8381,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C8" t="n">
@@ -8401,10 +8413,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C9" t="n">
@@ -8433,10 +8445,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43767</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C10" t="n">
@@ -8465,10 +8477,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43871</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C11" t="n">
@@ -8497,10 +8509,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C12" t="n">
@@ -8529,10 +8541,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C13" t="n">
@@ -8561,10 +8573,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44132</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C14" t="n">
@@ -8593,10 +8605,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44237</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C15" t="n">
@@ -8625,10 +8637,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C16" t="n">
@@ -8657,10 +8669,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C17" t="n">
@@ -8689,10 +8701,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C18" t="n">
@@ -8721,10 +8733,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44601</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C19" t="n">
@@ -8753,10 +8765,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44685</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C20" t="n">
@@ -8785,10 +8797,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44775</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C21" t="n">
@@ -8817,10 +8829,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44869</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44873</v>
       </c>
       <c r="C22" t="n">
@@ -8849,10 +8861,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44970</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="C23" t="n">
@@ -8881,10 +8893,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C24" t="n">
@@ -8913,10 +8925,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C25" t="n">
@@ -8945,10 +8957,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C26" t="n">
@@ -8977,10 +8989,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45335</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C27" t="n">
@@ -9009,10 +9021,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C28" t="n">
@@ -9041,10 +9053,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C29" t="n">
@@ -9073,10 +9085,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="C30" t="n">
@@ -9105,10 +9117,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45700</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C31" t="n">
@@ -9137,10 +9149,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C32" t="n">
@@ -9169,10 +9181,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C33" t="n">
@@ -9201,10 +9213,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45965</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C34" t="n">
@@ -9233,10 +9245,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C35" t="n">
@@ -9265,10 +9277,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C36" t="n">
@@ -9297,10 +9309,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C37" t="n">
@@ -9347,12 +9359,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/DD.xlsx
+++ b/salidas/empresas/DD.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.73949432373047</v>
+        <v>41.73948287963867</v>
       </c>
       <c r="C2" t="n">
         <v>75.57026672363281</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>42.45980834960938</v>
+        <v>42.45978927612305</v>
       </c>
       <c r="C3" t="n">
         <v>76.87443542480469</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>40.42570114135742</v>
+        <v>40.42571640014648</v>
       </c>
       <c r="C4" t="n">
         <v>72.53315734863281</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>40.43567276000977</v>
+        <v>40.43567657470703</v>
       </c>
       <c r="C5" t="n">
         <v>72.551025390625</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>39.69885635375977</v>
+        <v>39.6988639831543</v>
       </c>
       <c r="C6" t="n">
         <v>71.22899627685547</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>39.24927139282227</v>
+        <v>39.24927520751953</v>
       </c>
       <c r="C7" t="n">
         <v>69.72830963134766</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.77427673339844</v>
+        <v>34.77426910400391</v>
       </c>
       <c r="C8" t="n">
         <v>61.77824401855469</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.34423828125</v>
+        <v>38.34420013427734</v>
       </c>
       <c r="C9" t="n">
         <v>68.12042999267578</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>39.57281494140625</v>
+        <v>39.57280349731445</v>
       </c>
       <c r="C10" t="n">
         <v>69.63898468017578</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>41.41032409667969</v>
+        <v>41.41033554077148</v>
       </c>
       <c r="C11" t="n">
         <v>72.87260437011719</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.88764190673828</v>
+        <v>40.88763046264648</v>
       </c>
       <c r="C13" t="n">
         <v>71.2825927734375</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.56821441650391</v>
+        <v>42.56822967529297</v>
       </c>
       <c r="C14" t="n">
         <v>74.21250152587891</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>44.86369323730469</v>
+        <v>44.86367797851562</v>
       </c>
       <c r="C15" t="n">
         <v>78.21433258056641</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>47.37550735473633</v>
+        <v>47.37549591064453</v>
       </c>
       <c r="C16" t="n">
         <v>81.93031311035156</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>46.08420181274414</v>
+        <v>46.08420562744141</v>
       </c>
       <c r="C17" t="n">
         <v>79.69715118408203</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>46.879638671875</v>
+        <v>46.87964630126953</v>
       </c>
       <c r="C18" t="n">
         <v>81.07277679443359</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>46.11120223999023</v>
+        <v>46.11121368408203</v>
       </c>
       <c r="C19" t="n">
         <v>79.00040435791016</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>45.33411407470703</v>
+        <v>45.33412170410156</v>
       </c>
       <c r="C22" t="n">
         <v>76.92802429199219</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>44.15497207641602</v>
+        <v>44.15497970581055</v>
       </c>
       <c r="C24" t="n">
         <v>74.92711639404297</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>41.93228912353516</v>
+        <v>41.93228149414062</v>
       </c>
       <c r="C25" t="n">
         <v>70.42505645751953</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>41.10257339477539</v>
+        <v>41.10256958007812</v>
       </c>
       <c r="C26" t="n">
         <v>69.03156280517578</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>40.0920295715332</v>
+        <v>40.09203338623047</v>
       </c>
       <c r="C27" t="n">
         <v>67.33435821533203</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>39.63879776000977</v>
+        <v>39.63881301879883</v>
       </c>
       <c r="C28" t="n">
         <v>65.83367156982422</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>43.18854904174805</v>
+        <v>43.18854141235352</v>
       </c>
       <c r="C29" t="n">
         <v>71.72922515869141</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>37.98585891723633</v>
+        <v>37.98587417602539</v>
       </c>
       <c r="C31" t="n">
         <v>62.3677978515625</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>36.24490356445312</v>
+        <v>36.24488830566406</v>
       </c>
       <c r="C32" t="n">
         <v>59.50934982299805</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>37.13714218139648</v>
+        <v>37.13713836669922</v>
       </c>
       <c r="C33" t="n">
         <v>60.97430419921875</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>34.99851226806641</v>
+        <v>34.99851989746094</v>
       </c>
       <c r="C34" t="n">
         <v>56.77595520019531</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>29.38202667236328</v>
+        <v>29.38201904296875</v>
       </c>
       <c r="C35" t="n">
         <v>47.66464996337891</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.42865562438965</v>
+        <v>20.42866134643555</v>
       </c>
       <c r="C36" t="n">
         <v>33.14015197753906</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.98715019226074</v>
+        <v>16.98714256286621</v>
       </c>
       <c r="C37" t="n">
         <v>26.95875358581543</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.04712104797363</v>
+        <v>13.04711437225342</v>
       </c>
       <c r="C38" t="n">
         <v>20.70589447021484</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.060172080993652</v>
+        <v>8.06017017364502</v>
       </c>
       <c r="C39" t="n">
         <v>12.7915620803833</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>18.3045825958252</v>
+        <v>18.30457878112793</v>
       </c>
       <c r="C41" t="n">
         <v>28.58449745178223</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.22656631469727</v>
+        <v>20.22657012939453</v>
       </c>
       <c r="C42" t="n">
         <v>31.58586883544922</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>18.64082717895508</v>
+        <v>18.64081954956055</v>
       </c>
       <c r="C43" t="n">
         <v>28.8346118927002</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>24.45020484924316</v>
+        <v>24.45021057128906</v>
       </c>
       <c r="C44" t="n">
         <v>37.82086181640625</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.58879470825195</v>
+        <v>24.58879661560059</v>
       </c>
       <c r="C45" t="n">
         <v>38.03524780273438</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.28901863098145</v>
+        <v>30.28901672363281</v>
       </c>
       <c r="C46" t="n">
         <v>46.57486343383789</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.27986335754395</v>
+        <v>27.27986907958984</v>
       </c>
       <c r="C47" t="n">
         <v>41.94775009155273</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>32.2757453918457</v>
+        <v>32.27574157714844</v>
       </c>
       <c r="C48" t="n">
         <v>49.62983322143555</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>32.27127456665039</v>
+        <v>32.27126693725586</v>
       </c>
       <c r="C49" t="n">
         <v>49.36185455322266</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>31.64056205749512</v>
+        <v>31.64055442810059</v>
       </c>
       <c r="C50" t="n">
         <v>48.39712524414062</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>33.06549835205078</v>
+        <v>33.06547927856445</v>
       </c>
       <c r="C51" t="n">
         <v>50.57669448852539</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>34.71035385131836</v>
+        <v>34.71036148071289</v>
       </c>
       <c r="C52" t="n">
         <v>52.82772445678711</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>36.18939208984375</v>
+        <v>36.18938827514648</v>
       </c>
       <c r="C53" t="n">
         <v>55.07875442504883</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>31.58796119689941</v>
+        <v>31.58794784545898</v>
       </c>
       <c r="C54" t="n">
         <v>48.0755500793457</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.00926780700684</v>
+        <v>28.00927352905273</v>
       </c>
       <c r="C55" t="n">
         <v>42.37651824951172</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.27209091186523</v>
+        <v>32.27207565307617</v>
       </c>
       <c r="C56" t="n">
         <v>48.82589340209961</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>28.77682304382324</v>
+        <v>28.77682495117188</v>
       </c>
       <c r="C57" t="n">
         <v>43.53776168823242</v>
@@ -1562,7 +1562,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>32.60072708129883</v>
+        <v>32.60073471069336</v>
       </c>
       <c r="C58" t="n">
         <v>49.05814361572266</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>36.61349105834961</v>
+        <v>36.61349868774414</v>
       </c>
       <c r="C59" t="n">
         <v>55.09661865234375</v>
@@ -1619,7 +1619,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>40.70889282226562</v>
+        <v>40.70888519287109</v>
       </c>
       <c r="C61" t="n">
         <v>60.99217224121094</v>
@@ -1638,7 +1638,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>42.30672073364258</v>
+        <v>42.30671691894531</v>
       </c>
       <c r="C62" t="n">
         <v>63.38612365722656</v>
@@ -1657,7 +1657,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>44.30997467041016</v>
+        <v>44.30997085571289</v>
       </c>
       <c r="C63" t="n">
         <v>66.38749694824219</v>
@@ -1676,7 +1676,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>45.19652557373047</v>
+        <v>45.1965217590332</v>
       </c>
       <c r="C64" t="n">
         <v>67.44155120849609</v>
@@ -1695,7 +1695,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>49.07563781738281</v>
+        <v>49.07565307617188</v>
       </c>
       <c r="C65" t="n">
         <v>73.22991180419922</v>
@@ -1714,7 +1714,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.2569694519043</v>
+        <v>43.25695037841797</v>
       </c>
       <c r="C66" t="n">
         <v>64.54736328125</v>
@@ -1733,7 +1733,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>43.4104118347168</v>
+        <v>43.41041564941406</v>
       </c>
       <c r="C67" t="n">
         <v>64.31511688232422</v>
@@ -1752,7 +1752,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>42.04780960083008</v>
+        <v>42.04781341552734</v>
       </c>
       <c r="C68" t="n">
         <v>62.29633712768555</v>
@@ -1771,7 +1771,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>34.3062858581543</v>
+        <v>34.30628967285156</v>
       </c>
       <c r="C69" t="n">
         <v>50.82680892944336</v>
@@ -1790,7 +1790,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>27.35047912597656</v>
+        <v>27.3504695892334</v>
       </c>
       <c r="C70" t="n">
         <v>40.12548828125</v>
@@ -1809,7 +1809,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>33.95063400268555</v>
+        <v>33.95064163208008</v>
       </c>
       <c r="C71" t="n">
         <v>49.80848693847656</v>
@@ -1828,7 +1828,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>33.74361801147461</v>
+        <v>33.74362945556641</v>
       </c>
       <c r="C72" t="n">
         <v>49.50477600097656</v>
@@ -1866,7 +1866,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.16335678100586</v>
+        <v>41.16336059570312</v>
       </c>
       <c r="C74" t="n">
         <v>59.86665725708008</v>
@@ -1885,7 +1885,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>41.16335678100586</v>
+        <v>41.16336059570312</v>
       </c>
       <c r="C75" t="n">
         <v>59.86665725708008</v>
@@ -1904,7 +1904,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.85614776611328</v>
+        <v>42.85615158081055</v>
       </c>
       <c r="C76" t="n">
         <v>61.88543701171875</v>
@@ -1923,7 +1923,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>41.91590118408203</v>
+        <v>41.91588973999023</v>
       </c>
       <c r="C77" t="n">
         <v>60.52767181396484</v>
@@ -1980,7 +1980,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>35.97378158569336</v>
+        <v>35.97377395629883</v>
       </c>
       <c r="C80" t="n">
         <v>51.41636276245117</v>
@@ -2018,7 +2018,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>36.59184265136719</v>
+        <v>36.59185409545898</v>
       </c>
       <c r="C82" t="n">
         <v>51.73794174194336</v>
@@ -2037,7 +2037,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>37.02144622802734</v>
+        <v>37.02145004272461</v>
       </c>
       <c r="C83" t="n">
         <v>52.34535980224609</v>
@@ -2056,7 +2056,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>38.14596557617188</v>
+        <v>38.14596939086914</v>
       </c>
       <c r="C84" t="n">
         <v>53.93537139892578</v>
@@ -2075,7 +2075,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>41.25703430175781</v>
+        <v>41.25704956054688</v>
       </c>
       <c r="C85" t="n">
         <v>57.75854873657227</v>
@@ -2094,7 +2094,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>41.09114837646484</v>
+        <v>41.09114456176758</v>
       </c>
       <c r="C86" t="n">
         <v>57.52629852294922</v>
@@ -2113,7 +2113,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>40.47859954833984</v>
+        <v>40.47861480712891</v>
       </c>
       <c r="C87" t="n">
         <v>56.66876602172852</v>
@@ -2132,7 +2132,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>41.03843688964844</v>
+        <v>41.03844451904297</v>
       </c>
       <c r="C88" t="n">
         <v>56.88314819335938</v>
@@ -2170,7 +2170,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.41533279418945</v>
+        <v>44.41534805297852</v>
       </c>
       <c r="C90" t="n">
         <v>61.56386184692383</v>
@@ -2189,7 +2189,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>41.87609481811523</v>
+        <v>41.87607955932617</v>
       </c>
       <c r="C91" t="n">
         <v>57.47270584106445</v>
@@ -2227,7 +2227,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.68405151367188</v>
+        <v>48.68405914306641</v>
       </c>
       <c r="C93" t="n">
         <v>66.81626129150391</v>
@@ -2246,7 +2246,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.39030075073242</v>
+        <v>50.39029312133789</v>
       </c>
       <c r="C94" t="n">
         <v>68.60279083251953</v>
@@ -2284,7 +2284,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.25638961791992</v>
+        <v>51.25637435913086</v>
       </c>
       <c r="C96" t="n">
         <v>69.78190612792969</v>
@@ -2322,7 +2322,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>60.14943313598633</v>
+        <v>60.14944458007812</v>
       </c>
       <c r="C98" t="n">
         <v>81.30503082275391</v>
@@ -2341,7 +2341,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>64.37880706787109</v>
+        <v>64.37881469726562</v>
       </c>
       <c r="C99" t="n">
         <v>87.02192687988281</v>
@@ -2360,7 +2360,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>64.70454406738281</v>
+        <v>64.70453643798828</v>
       </c>
       <c r="C100" t="n">
         <v>86.80754089355469</v>
@@ -2398,7 +2398,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>69.40522766113281</v>
+        <v>69.40523529052734</v>
       </c>
       <c r="C102" t="n">
         <v>93.11399841308594</v>
@@ -2417,7 +2417,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>69.01171112060547</v>
+        <v>69.01168060302734</v>
       </c>
       <c r="C103" t="n">
         <v>91.93489074707031</v>
@@ -2436,7 +2436,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>68.48869323730469</v>
+        <v>68.48870086669922</v>
       </c>
       <c r="C104" t="n">
         <v>91.23814392089844</v>
@@ -2455,7 +2455,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>71.81455993652344</v>
+        <v>71.81454467773438</v>
       </c>
       <c r="C105" t="n">
         <v>95.66873931884766</v>
@@ -2474,7 +2474,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.81914520263672</v>
+        <v>70.81912231445312</v>
       </c>
       <c r="C106" t="n">
         <v>93.68569183349609</v>
@@ -2512,7 +2512,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.72782897949219</v>
+        <v>65.72784423828125</v>
       </c>
       <c r="C108" t="n">
         <v>86.95046997070312</v>
@@ -2531,7 +2531,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>62.15701293945312</v>
+        <v>62.15704727172852</v>
       </c>
       <c r="C109" t="n">
         <v>81.48368072509766</v>
@@ -2550,7 +2550,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>61.54378128051758</v>
+        <v>61.54377365112305</v>
       </c>
       <c r="C110" t="n">
         <v>80.67974090576172</v>
@@ -2569,7 +2569,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>67.10398864746094</v>
+        <v>67.10397338867188</v>
       </c>
       <c r="C111" t="n">
         <v>87.96878814697266</v>
@@ -2607,7 +2607,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>70.13105010986328</v>
+        <v>70.13108062744141</v>
       </c>
       <c r="C113" t="n">
         <v>91.11308288574219</v>
@@ -2626,7 +2626,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>71.60247039794922</v>
+        <v>71.60243225097656</v>
       </c>
       <c r="C114" t="n">
         <v>93.02467346191406</v>
@@ -2645,7 +2645,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>70.924560546875</v>
+        <v>70.92455291748047</v>
       </c>
       <c r="C115" t="n">
         <v>91.41679382324219</v>
@@ -2664,7 +2664,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>65.22786712646484</v>
+        <v>65.22785949707031</v>
       </c>
       <c r="C116" t="n">
         <v>84.07415008544922</v>
@@ -2683,7 +2683,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>60.65386962890625</v>
+        <v>60.65386199951172</v>
       </c>
       <c r="C117" t="n">
         <v>78.17859649658203</v>
@@ -2702,7 +2702,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>59.3579216003418</v>
+        <v>59.35792922973633</v>
       </c>
       <c r="C118" t="n">
         <v>75.74891662597656</v>
@@ -2740,7 +2740,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>72.97943878173828</v>
+        <v>72.97946166992188</v>
       </c>
       <c r="C120" t="n">
         <v>93.13186645507812</v>
@@ -2759,7 +2759,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>72.70982360839844</v>
+        <v>72.70983123779297</v>
       </c>
       <c r="C121" t="n">
         <v>91.97061920166016</v>
@@ -2778,7 +2778,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>59.32037734985352</v>
+        <v>59.32038497924805</v>
       </c>
       <c r="C122" t="n">
         <v>75.0343017578125</v>
@@ -2797,7 +2797,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>68.65629577636719</v>
+        <v>68.65628814697266</v>
       </c>
       <c r="C123" t="n">
         <v>86.84327697753906</v>
@@ -2816,7 +2816,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>72.48080444335938</v>
+        <v>72.48081970214844</v>
       </c>
       <c r="C124" t="n">
         <v>90.86296844482422</v>
@@ -2835,7 +2835,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>74.97476196289062</v>
+        <v>74.97476959228516</v>
       </c>
       <c r="C125" t="n">
         <v>93.98940277099609</v>
@@ -2854,7 +2854,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>73.19337463378906</v>
+        <v>73.193359375</v>
       </c>
       <c r="C126" t="n">
         <v>91.75623321533203</v>
@@ -2873,7 +2873,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>71.50013732910156</v>
+        <v>71.5001220703125</v>
       </c>
       <c r="C127" t="n">
         <v>88.80845642089844</v>
@@ -2892,7 +2892,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>77.19596862792969</v>
+        <v>77.19597625732422</v>
       </c>
       <c r="C128" t="n">
         <v>95.88312530517578</v>
@@ -2911,7 +2911,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>77.15281677246094</v>
+        <v>77.15283203125</v>
       </c>
       <c r="C129" t="n">
         <v>95.82952880859375</v>
@@ -2930,7 +2930,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>75.20750427246094</v>
+        <v>75.20749664306641</v>
       </c>
       <c r="C130" t="n">
         <v>92.59590148925781</v>
@@ -2949,7 +2949,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>78.08059692382812</v>
+        <v>78.08056640625</v>
       </c>
       <c r="C131" t="n">
         <v>96.13323974609375</v>
@@ -2968,7 +2968,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>80.85206604003906</v>
+        <v>80.85205841064453</v>
       </c>
       <c r="C132" t="n">
         <v>99.54550933837891</v>
@@ -2987,7 +2987,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>83.68385314941406</v>
+        <v>83.68386077880859</v>
       </c>
       <c r="C133" t="n">
         <v>102.2253112792969</v>
@@ -3006,7 +3006,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>87.20845794677734</v>
+        <v>87.20847320556641</v>
       </c>
       <c r="C134" t="n">
         <v>106.5308456420898</v>
@@ -3044,7 +3044,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>93.58914184570312</v>
+        <v>93.58916473388672</v>
       </c>
       <c r="C136" t="n">
         <v>113.5161819458008</v>
@@ -3082,7 +3082,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>91.26192474365234</v>
+        <v>91.26195526123047</v>
       </c>
       <c r="C138" t="n">
         <v>110.6934661865234</v>
@@ -3101,7 +3101,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>93.57916259765625</v>
+        <v>93.57917785644531</v>
       </c>
       <c r="C139" t="n">
         <v>112.676513671875</v>
@@ -3120,7 +3120,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>95.97986602783203</v>
+        <v>95.97985076904297</v>
       </c>
       <c r="C140" t="n">
         <v>114.7667541503906</v>
@@ -3139,7 +3139,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>99.58058166503906</v>
+        <v>99.58060455322266</v>
       </c>
       <c r="C141" t="n">
         <v>119.0722961425781</v>
@@ -3158,7 +3158,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>103.4353256225586</v>
+        <v>103.4353179931641</v>
       </c>
       <c r="C142" t="n">
         <v>123.6815490722656</v>
@@ -3177,7 +3177,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>108.0371017456055</v>
+        <v>108.0371170043945</v>
       </c>
       <c r="C143" t="n">
         <v>129.1840667724609</v>
@@ -3196,7 +3196,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>108.09716796875</v>
+        <v>108.0971603393555</v>
       </c>
       <c r="C144" t="n">
         <v>128.5587768554688</v>
@@ -3221,7 +3221,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>106.9855499267578</v>
+        <v>106.9855651855469</v>
       </c>
       <c r="C145" t="n">
         <v>127.2367401123047</v>
@@ -3246,7 +3246,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>113.5350646972656</v>
+        <v>113.5350875854492</v>
       </c>
       <c r="C146" t="n">
         <v>135.0260162353516</v>
@@ -3271,7 +3271,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>106.1481857299805</v>
+        <v>106.1481781005859</v>
       </c>
       <c r="C147" t="n">
         <v>125.593132019043</v>
@@ -3321,7 +3321,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>95.48807525634766</v>
+        <v>95.48808288574219</v>
       </c>
       <c r="C149" t="n">
         <v>112.980224609375</v>
@@ -3346,7 +3346,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>97.38043212890625</v>
+        <v>97.38043975830078</v>
       </c>
       <c r="C150" t="n">
         <v>114.5345077514648</v>
@@ -3371,7 +3371,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>100.1297607421875</v>
+        <v>100.129768371582</v>
       </c>
       <c r="C151" t="n">
         <v>117.7681274414062</v>
@@ -3396,7 +3396,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>104.4587936401367</v>
+        <v>104.4587707519531</v>
       </c>
       <c r="C152" t="n">
         <v>122.8597412109375</v>
@@ -3450,7 +3450,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>98.20658874511719</v>
+        <v>98.20661163330078</v>
       </c>
       <c r="C154" t="n">
         <v>114.8918151855469</v>
@@ -3479,7 +3479,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>82.34025573730469</v>
+        <v>82.34026336669922</v>
       </c>
       <c r="C155" t="n">
         <v>96.32975769042969</v>
@@ -3508,7 +3508,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>88.93226623535156</v>
+        <v>88.93225860595703</v>
       </c>
       <c r="C156" t="n">
         <v>103.3508224487305</v>
@@ -3537,7 +3537,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>82.21429443359375</v>
+        <v>82.21431732177734</v>
       </c>
       <c r="C157" t="n">
         <v>95.54367828369141</v>
@@ -3566,7 +3566,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>82.72161102294922</v>
+        <v>82.72159576416016</v>
       </c>
       <c r="C158" t="n">
         <v>96.13323974609375</v>
@@ -3595,7 +3595,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>82.39027404785156</v>
+        <v>82.39026641845703</v>
       </c>
       <c r="C159" t="n">
         <v>95.0970458984375</v>
@@ -3624,7 +3624,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>82.51409149169922</v>
+        <v>82.51408386230469</v>
       </c>
       <c r="C160" t="n">
         <v>95.23996734619141</v>
@@ -3653,7 +3653,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>88.49662017822266</v>
+        <v>88.49662780761719</v>
       </c>
       <c r="C161" t="n">
         <v>102.1451797485352</v>
@@ -3682,7 +3682,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>70.50948333740234</v>
+        <v>70.50950622558594</v>
       </c>
       <c r="C162" t="n">
         <v>81.07856750488281</v>
@@ -3740,7 +3740,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>79.09474182128906</v>
+        <v>79.09475708007812</v>
       </c>
       <c r="C164" t="n">
         <v>90.57740783691406</v>
@@ -3769,7 +3769,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>74.45822906494141</v>
+        <v>74.45823669433594</v>
       </c>
       <c r="C165" t="n">
         <v>85.26778411865234</v>
@@ -3798,7 +3798,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>78.16307830810547</v>
+        <v>78.1630859375</v>
       </c>
       <c r="C166" t="n">
         <v>89.51045989990234</v>
@@ -3827,7 +3827,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>72.24411010742188</v>
+        <v>72.24410247802734</v>
       </c>
       <c r="C167" t="n">
         <v>82.73221588134766</v>
@@ -3856,7 +3856,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>71.36743927001953</v>
+        <v>71.36742401123047</v>
       </c>
       <c r="C168" t="n">
         <v>81.35146331787109</v>
@@ -3885,7 +3885,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>70.69573211669922</v>
+        <v>70.69571685791016</v>
       </c>
       <c r="C169" t="n">
         <v>80.58577728271484</v>
@@ -3914,7 +3914,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>56.35836791992188</v>
+        <v>56.35835647583008</v>
       </c>
       <c r="C170" t="n">
         <v>64.24267578125</v>
@@ -3943,7 +3943,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.54239654541016</v>
+        <v>47.54237747192383</v>
       </c>
       <c r="C171" t="n">
         <v>53.84937286376953</v>
@@ -3972,7 +3972,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>37.79010009765625</v>
+        <v>37.79010772705078</v>
       </c>
       <c r="C172" t="n">
         <v>42.80334854125977</v>
@@ -4001,7 +4001,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>52.10823059082031</v>
+        <v>52.10821914672852</v>
       </c>
       <c r="C173" t="n">
         <v>59.02091979980469</v>
@@ -4057,7 +4057,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>59.23871994018555</v>
+        <v>59.23872375488281</v>
       </c>
       <c r="C175" t="n">
         <v>66.69037628173828</v>
@@ -4084,7 +4084,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>59.95292663574219</v>
+        <v>59.95291900634766</v>
       </c>
       <c r="C176" t="n">
         <v>67.12970733642578</v>
@@ -4111,7 +4111,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>62.50886154174805</v>
+        <v>62.50888442993164</v>
       </c>
       <c r="C177" t="n">
         <v>69.99163055419922</v>
@@ -4138,7 +4138,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>62.19499588012695</v>
+        <v>62.19501876831055</v>
       </c>
       <c r="C178" t="n">
         <v>69.64016723632812</v>
@@ -4165,7 +4165,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>63.76443481445312</v>
+        <v>63.76443862915039</v>
       </c>
       <c r="C179" t="n">
         <v>71.39749145507812</v>
@@ -4192,7 +4192,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>71.44876861572266</v>
+        <v>71.44874572753906</v>
       </c>
       <c r="C180" t="n">
         <v>79.63179779052734</v>
@@ -4246,7 +4246,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>89.47987365722656</v>
+        <v>89.47986602783203</v>
       </c>
       <c r="C182" t="n">
         <v>99.72803497314453</v>
@@ -4273,7 +4273,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>79.53939819335938</v>
+        <v>79.53937530517578</v>
       </c>
       <c r="C183" t="n">
         <v>88.26778411865234</v>
@@ -4300,7 +4300,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>87.41189575195312</v>
+        <v>87.41188049316406</v>
       </c>
       <c r="C184" t="n">
         <v>97.00418090820312</v>
@@ -4327,7 +4327,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>87.21959686279297</v>
+        <v>87.21961212158203</v>
       </c>
       <c r="C185" t="n">
         <v>96.79079437255859</v>
@@ -4412,7 +4412,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>85.54106903076172</v>
+        <v>85.54107666015625</v>
       </c>
       <c r="C188" t="n">
         <v>94.20502471923828</v>
@@ -4441,7 +4441,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>84.3670654296875</v>
+        <v>84.36705780029297</v>
       </c>
       <c r="C189" t="n">
         <v>92.91213226318359</v>
@@ -4470,7 +4470,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>77.494140625</v>
+        <v>77.49415588378906</v>
       </c>
       <c r="C190" t="n">
         <v>85.34309387207031</v>
@@ -4499,7 +4499,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>79.32920837402344</v>
+        <v>79.3292236328125</v>
       </c>
       <c r="C191" t="n">
         <v>87.364013671875</v>
@@ -4528,7 +4528,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>84.62857818603516</v>
+        <v>84.62858581542969</v>
       </c>
       <c r="C192" t="n">
         <v>92.83682250976562</v>
@@ -4586,7 +4586,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>87.64939117431641</v>
+        <v>87.64940643310547</v>
       </c>
       <c r="C194" t="n">
         <v>96.15062713623047</v>
@@ -4644,7 +4644,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>84.56304931640625</v>
+        <v>84.56304168701172</v>
       </c>
       <c r="C196" t="n">
         <v>92.35983276367188</v>
@@ -4673,7 +4673,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>75.77117156982422</v>
+        <v>75.77114868164062</v>
       </c>
       <c r="C197" t="n">
         <v>82.75732421875</v>
@@ -4702,7 +4702,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>78.36159515380859</v>
+        <v>78.36158752441406</v>
       </c>
       <c r="C198" t="n">
         <v>85.16736602783203</v>
@@ -4731,7 +4731,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>64.19068145751953</v>
+        <v>64.190673828125</v>
       </c>
       <c r="C199" t="n">
         <v>69.76569366455078</v>
@@ -4760,7 +4760,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>71.11083984375</v>
+        <v>71.11086273193359</v>
       </c>
       <c r="C200" t="n">
         <v>76.85774230957031</v>
@@ -4789,7 +4789,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>64.6187744140625</v>
+        <v>64.61875915527344</v>
       </c>
       <c r="C201" t="n">
         <v>69.84100341796875</v>
@@ -4818,7 +4818,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.53318405151367</v>
+        <v>58.53318023681641</v>
       </c>
       <c r="C202" t="n">
         <v>63.26359939575195</v>
@@ -4847,7 +4847,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>66.43052673339844</v>
+        <v>66.43051147460938</v>
       </c>
       <c r="C203" t="n">
         <v>71.79916381835938</v>
@@ -4876,7 +4876,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>82.2799072265625</v>
+        <v>82.27991485595703</v>
       </c>
       <c r="C204" t="n">
         <v>88.50627899169922</v>
@@ -4905,7 +4905,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>80.08609771728516</v>
+        <v>80.08609008789062</v>
       </c>
       <c r="C205" t="n">
         <v>86.14644622802734</v>
@@ -4934,7 +4934,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>86.29414367675781</v>
+        <v>86.29412078857422</v>
       </c>
       <c r="C206" t="n">
         <v>92.82426452636719</v>
@@ -4992,7 +4992,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>84.165771484375</v>
+        <v>84.16576385498047</v>
       </c>
       <c r="C208" t="n">
         <v>90.08786773681641</v>
@@ -5021,7 +5021,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>81.76168823242188</v>
+        <v>81.76169586181641</v>
       </c>
       <c r="C209" t="n">
         <v>87.51464080810547</v>
@@ -5079,7 +5079,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>84.22731781005859</v>
+        <v>84.22730255126953</v>
       </c>
       <c r="C211" t="n">
         <v>89.67363739013672</v>
@@ -5108,7 +5108,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>91.95071411132812</v>
+        <v>91.95070648193359</v>
       </c>
       <c r="C212" t="n">
         <v>97.44351196289062</v>
@@ -5137,7 +5137,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>91.07418060302734</v>
+        <v>91.07419586181641</v>
       </c>
       <c r="C213" t="n">
         <v>96.51464080810547</v>
@@ -5195,7 +5195,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>86.32447052001953</v>
+        <v>86.32444763183594</v>
       </c>
       <c r="C215" t="n">
         <v>91.48117065429688</v>
@@ -5224,7 +5224,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>85.16733551025391</v>
+        <v>85.16732788085938</v>
       </c>
       <c r="C216" t="n">
         <v>89.79916381835938</v>
@@ -5253,7 +5253,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>91.58406066894531</v>
+        <v>91.58406829833984</v>
       </c>
       <c r="C217" t="n">
         <v>96.56485748291016</v>
@@ -5282,7 +5282,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>73.57199859619141</v>
+        <v>73.57200622558594</v>
       </c>
       <c r="C218" t="n">
         <v>77.57321929931641</v>
@@ -5340,7 +5340,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>91.77560424804688</v>
+        <v>91.77561187744141</v>
       </c>
       <c r="C220" t="n">
         <v>96.23849487304688</v>
@@ -5369,7 +5369,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>86.78401947021484</v>
+        <v>86.78403472900391</v>
       </c>
       <c r="C221" t="n">
         <v>91.00418090820312</v>
@@ -5427,7 +5427,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>96.79778289794922</v>
+        <v>96.79777526855469</v>
       </c>
       <c r="C223" t="n">
         <v>101.0334701538086</v>
@@ -5456,7 +5456,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>100.6581497192383</v>
+        <v>100.6581573486328</v>
       </c>
       <c r="C224" t="n">
         <v>105.0627593994141</v>
@@ -5485,7 +5485,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>101.7832565307617</v>
+        <v>101.7832412719727</v>
       </c>
       <c r="C225" t="n">
         <v>105.7531356811523</v>
@@ -5543,7 +5543,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>100.2610321044922</v>
+        <v>100.2610397338867</v>
       </c>
       <c r="C227" t="n">
         <v>104.1715469360352</v>
@@ -5572,7 +5572,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>101.4453506469727</v>
+        <v>101.4453430175781</v>
       </c>
       <c r="C228" t="n">
         <v>104.9246826171875</v>
@@ -5800,7 +5800,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>88.22238922119141</v>
+        <v>88.22239685058594</v>
       </c>
       <c r="C236" t="n">
         <v>90.25104522705078</v>
@@ -5827,7 +5827,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>94.88312530517578</v>
+        <v>94.88313293457031</v>
       </c>
       <c r="C237" t="n">
         <v>96.55229949951172</v>
